--- a/Задание/ПУ/Модуль 1/import/Пункты выдачи_import.xlsx
+++ b/Задание/ПУ/Модуль 1/import/Пункты выдачи_import.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\st53\Desktop\Прил_ОЗ_КОД 09.02.07-2-2026\ПУ\Модуль 1\Прил_2_ОЗ_КОД 09.02.07-2-2026-М1\import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Новая папка (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="990" windowWidth="26760" windowHeight="16560"/>
+    <workbookView xWindow="1764" yWindow="996" windowWidth="26760" windowHeight="16560"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -498,294 +498,186 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A36"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>20</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>21</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>22</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>23</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>24</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>27</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>28</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>29</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>35</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>36</v>
-      </c>
-      <c r="B36" s="1" t="s">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
     </row>
